--- a/Result KIDSFEST - CAT 2.xlsx
+++ b/Result KIDSFEST - CAT 2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\TECHOSA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B97F9CC-EE1B-436B-869A-8E16D958DEDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D010422F-8940-4EE8-BC14-C4DB69A9C9D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="884" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="884" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="201" sheetId="1" r:id="rId1"/>
@@ -2490,6 +2490,12 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2498,12 +2504,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -6592,18 +6592,18 @@
       <c r="F11" s="94"/>
     </row>
     <row r="12" spans="1:6" ht="39.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="98" t="s">
+      <c r="A12" s="100" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="99"/>
-      <c r="C12" s="100"/>
+      <c r="B12" s="101"/>
+      <c r="C12" s="102"/>
       <c r="D12" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="E12" s="98" t="s">
+      <c r="E12" s="100" t="s">
         <v>23</v>
       </c>
-      <c r="F12" s="100"/>
+      <c r="F12" s="102"/>
     </row>
     <row r="13" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="8"/>
@@ -8386,7 +8386,7 @@
         <v>18</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="G19" s="75"/>
     </row>
@@ -10103,10 +10103,10 @@
       <c r="E18" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="F18" s="101" t="s">
+      <c r="F18" s="98" t="s">
         <v>269</v>
       </c>
-      <c r="G18" s="102"/>
+      <c r="G18" s="99"/>
     </row>
     <row r="19" spans="1:7" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
